--- a/CHIK_MORBID/03_Output/tables/core3_descriptive_tables.xlsx
+++ b/CHIK_MORBID/03_Output/tables/core3_descriptive_tables.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -78,6 +78,9 @@
     <t xml:space="preserve">6b. -&gt; death_cohort: + death status known</t>
   </si>
   <si>
+    <t xml:space="preserve">  983,947</t>
+  </si>
+  <si>
     <t xml:space="preserve">condition</t>
   </si>
   <si>
@@ -297,10 +300,13 @@
     <t xml:space="preserve">  1,270 (0.2%)</t>
   </si>
   <si>
-    <t xml:space="preserve">655,585 (61.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419,211 (39.0%)</t>
+    <t xml:space="preserve">983,947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600,128 (61.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">383,819 (39.0%)</t>
   </si>
   <si>
     <t xml:space="preserve">Died from chikungunya</t>
@@ -309,37 +315,37 @@
     <t xml:space="preserve">1,050 (0.1%)</t>
   </si>
   <si>
-    <t xml:space="preserve">49,767 (4.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120,904 (11.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,899 (0.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">935,038 (87.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 16,688 (1.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 87,125 (8.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1,826 (0.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 31,046 (2.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    340 (0.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1,040 (0.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  1,693 (0.2%)</t>
+    <t xml:space="preserve">45,529 (4.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110,350 (11.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,412 (0.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">856,342 (87.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 15,302 (1.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 79,512 (8.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1,640 (0.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28,379 (2.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    313 (0.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    924 (0.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1,535 (0.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">age_band</t>
@@ -786,10 +792,10 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>91.5</v>
       </c>
     </row>
   </sheetData>
@@ -805,50 +811,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="C2" t="n">
-        <v>447</v>
+        <v>397</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="C3" t="n">
-        <v>652</v>
+        <v>608</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E3" t="n">
         <v>0.55</v>
@@ -856,220 +862,220 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="C4" t="n">
-        <v>1424</v>
+        <v>1294</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E4" t="n">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="C5" t="n">
-        <v>2877</v>
+        <v>2624</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="C6" t="n">
-        <v>6874</v>
+        <v>6344</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E6" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="C7" t="n">
-        <v>12275</v>
+        <v>11236</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E7" t="n">
-        <v>7.83</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="C8" t="n">
-        <v>13796</v>
+        <v>12650</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E8" t="n">
-        <v>12.4</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="C9" t="n">
-        <v>8414</v>
+        <v>7638</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="n">
-        <v>14.54</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="C10" t="n">
-        <v>2717</v>
+        <v>2473</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" t="n">
-        <v>13.58</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="C11" t="n">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" t="n">
-        <v>10.22</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="C12" t="n">
-        <v>663</v>
+        <v>595</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="C13" t="n">
-        <v>718</v>
+        <v>634</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="C14" t="n">
-        <v>2724</v>
+        <v>2464</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E14" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="C15" t="n">
-        <v>8007</v>
+        <v>7256</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E15" t="n">
-        <v>4.37</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="C16" t="n">
-        <v>19751</v>
+        <v>18095</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E16" t="n">
         <v>10.73</v>
@@ -1077,101 +1083,101 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="C17" t="n">
-        <v>30640</v>
+        <v>27954</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E17" t="n">
-        <v>19.55</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="C18" t="n">
-        <v>31107</v>
+        <v>28365</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E18" t="n">
-        <v>27.95</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="C19" t="n">
-        <v>19385</v>
+        <v>17710</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E19" t="n">
-        <v>33.49</v>
+        <v>33.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="C20" t="n">
-        <v>6997</v>
+        <v>6443</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E20" t="n">
-        <v>34.97</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="C21" t="n">
-        <v>912</v>
+        <v>834</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E21" t="n">
-        <v>32.03</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="C22" t="n">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E22" t="n">
         <v>0.28</v>
@@ -1179,16 +1185,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="C23" t="n">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E23" t="n">
         <v>0.26</v>
@@ -1196,16 +1202,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="C24" t="n">
-        <v>467</v>
+        <v>429</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E24" t="n">
         <v>0.27</v>
@@ -1213,16 +1219,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="C25" t="n">
-        <v>574</v>
+        <v>520</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E25" t="n">
         <v>0.31</v>
@@ -1230,104 +1236,104 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="C26" t="n">
-        <v>755</v>
+        <v>681</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E26" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="C27" t="n">
-        <v>883</v>
+        <v>782</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E27" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="C28" t="n">
-        <v>798</v>
+        <v>723</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E28" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="C29" t="n">
-        <v>566</v>
+        <v>508</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E29" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="C30" t="n">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E30" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="C31" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>
@@ -1343,84 +1349,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
-        <v>64629</v>
+        <v>58929</v>
       </c>
       <c r="D2" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="E2" t="n">
-        <v>98.43</v>
+        <v>98.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="D3" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="E3" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>462</v>
+        <v>412</v>
       </c>
       <c r="D4" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="n">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D5" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="E5" t="n">
         <v>0.16</v>
@@ -1428,16 +1434,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D6" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="E6" t="n">
         <v>0.19</v>
@@ -1445,16 +1451,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="E7" t="n">
         <v>0.01</v>
@@ -1462,16 +1468,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="E8" t="n">
         <v>0.02</v>
@@ -1479,16 +1485,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D9" t="n">
-        <v>65658</v>
+        <v>59843</v>
       </c>
       <c r="E9" t="n">
         <v>0.1</v>
@@ -1496,84 +1502,84 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>117862</v>
+        <v>108444</v>
       </c>
       <c r="D10" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="E10" t="n">
-        <v>98.86</v>
+        <v>98.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="D11" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="E11" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="n">
-        <v>519</v>
+        <v>453</v>
       </c>
       <c r="D12" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="E12" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="n">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D13" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="E13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="E14" t="n">
         <v>0.06</v>
@@ -1581,16 +1587,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="E15" t="n">
         <v>0.01</v>
@@ -1598,16 +1604,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="E16" t="n">
         <v>0.01</v>
@@ -1615,16 +1621,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>119223</v>
+        <v>109678</v>
       </c>
       <c r="E17" t="n">
         <v>0.09</v>
@@ -1632,67 +1638,67 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" t="n">
-        <v>169931</v>
+        <v>156412</v>
       </c>
       <c r="D18" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="E18" t="n">
-        <v>97.75</v>
+        <v>97.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" t="n">
-        <v>938</v>
+        <v>851</v>
       </c>
       <c r="D19" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="E19" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>2220</v>
+        <v>2006</v>
       </c>
       <c r="D20" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="E20" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" t="n">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="D21" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="E21" t="n">
         <v>0.13</v>
@@ -1700,16 +1706,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="n">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="D22" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="E22" t="n">
         <v>0.16</v>
@@ -1717,16 +1723,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="E23" t="n">
         <v>0.01</v>
@@ -1734,16 +1740,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D24" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="E24" t="n">
         <v>0.02</v>
@@ -1751,16 +1757,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" t="n">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D25" t="n">
-        <v>173838</v>
+        <v>159952</v>
       </c>
       <c r="E25" t="n">
         <v>0.11</v>
@@ -1768,33 +1774,33 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" t="n">
-        <v>173235</v>
+        <v>158804</v>
       </c>
       <c r="D26" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="E26" t="n">
-        <v>94.55</v>
+        <v>94.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" t="n">
-        <v>1686</v>
+        <v>1547</v>
       </c>
       <c r="D27" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="E27" t="n">
         <v>0.92</v>
@@ -1802,33 +1808,33 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" t="n">
-        <v>6777</v>
+        <v>6142</v>
       </c>
       <c r="D28" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="E28" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" t="n">
-        <v>265</v>
+        <v>240</v>
       </c>
       <c r="D29" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="E29" t="n">
         <v>0.14</v>
@@ -1836,16 +1842,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C30" t="n">
-        <v>958</v>
+        <v>867</v>
       </c>
       <c r="D30" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="E30" t="n">
         <v>0.52</v>
@@ -1853,16 +1859,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D31" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="E31" t="n">
         <v>0.02</v>
@@ -1870,16 +1876,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D32" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="E32" t="n">
         <v>0.04</v>
@@ -1887,16 +1893,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C33" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="D33" t="n">
-        <v>183230</v>
+        <v>167880</v>
       </c>
       <c r="E33" t="n">
         <v>0.11</v>
@@ -1904,67 +1910,67 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" t="n">
-        <v>160736</v>
+        <v>147246</v>
       </c>
       <c r="D34" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="E34" t="n">
-        <v>87.33</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" t="n">
-        <v>3218</v>
+        <v>2979</v>
       </c>
       <c r="D35" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="E35" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" t="n">
-        <v>15976</v>
+        <v>14617</v>
       </c>
       <c r="D36" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="E36" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" t="n">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="D37" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="E37" t="n">
         <v>0.17</v>
@@ -1972,33 +1978,33 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" t="n">
-        <v>3377</v>
+        <v>3116</v>
       </c>
       <c r="D38" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="E38" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="E39" t="n">
         <v>0.02</v>
@@ -2006,33 +2012,33 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D40" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="E40" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" t="n">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="D41" t="n">
-        <v>184062</v>
+        <v>168639</v>
       </c>
       <c r="E41" t="n">
         <v>0.13</v>
@@ -2040,101 +2046,101 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C42" t="n">
-        <v>121436</v>
+        <v>110675</v>
       </c>
       <c r="D42" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="E42" t="n">
-        <v>77.47</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" t="n">
-        <v>4271</v>
+        <v>3916</v>
       </c>
       <c r="D43" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="E43" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C44" t="n">
-        <v>22514</v>
+        <v>20535</v>
       </c>
       <c r="D44" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="E44" t="n">
-        <v>14.36</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C45" t="n">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="D45" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C46" t="n">
-        <v>7644</v>
+        <v>6997</v>
       </c>
       <c r="D46" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="E46" t="n">
-        <v>4.88</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D47" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="E47" t="n">
         <v>0.06</v>
@@ -2142,101 +2148,101 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C48" t="n">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="D48" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="E48" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C49" t="n">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="D49" t="n">
-        <v>156748</v>
+        <v>142905</v>
       </c>
       <c r="E49" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C50" t="n">
-        <v>76357</v>
+        <v>69554</v>
       </c>
       <c r="D50" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="E50" t="n">
-        <v>68.6</v>
+        <v>68.57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>3549</v>
+        <v>3253</v>
       </c>
       <c r="D51" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="E51" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C52" t="n">
-        <v>20711</v>
+        <v>18841</v>
       </c>
       <c r="D52" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="E52" t="n">
-        <v>18.61</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C53" t="n">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="D53" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="E53" t="n">
         <v>0.21</v>
@@ -2244,33 +2250,33 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C54" t="n">
-        <v>9887</v>
+        <v>9063</v>
       </c>
       <c r="D54" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="E54" t="n">
-        <v>8.88</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C55" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D55" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="E55" t="n">
         <v>0.05</v>
@@ -2278,16 +2284,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C56" t="n">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="D56" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="E56" t="n">
         <v>0.18</v>
@@ -2295,118 +2301,118 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C57" t="n">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="D57" t="n">
-        <v>111302</v>
+        <v>101434</v>
       </c>
       <c r="E57" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C58" t="n">
-        <v>36586</v>
+        <v>33247</v>
       </c>
       <c r="D58" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="E58" t="n">
-        <v>63.21</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C59" t="n">
-        <v>1730</v>
+        <v>1569</v>
       </c>
       <c r="D59" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="E59" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C60" t="n">
-        <v>12579</v>
+        <v>11538</v>
       </c>
       <c r="D60" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="E60" t="n">
-        <v>21.73</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C61" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D61" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="E61" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C62" t="n">
-        <v>6420</v>
+        <v>5825</v>
       </c>
       <c r="D62" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="E62" t="n">
-        <v>11.09</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D63" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="E63" t="n">
         <v>0.1</v>
@@ -2414,33 +2420,33 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C64" t="n">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="D64" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="E64" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C65" t="n">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="D65" t="n">
-        <v>57881</v>
+        <v>52687</v>
       </c>
       <c r="E65" t="n">
         <v>0.36</v>
@@ -2448,101 +2454,101 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C66" t="n">
-        <v>12402</v>
+        <v>11320</v>
       </c>
       <c r="D66" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="E66" t="n">
-        <v>61.99</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C67" t="n">
-        <v>520</v>
+        <v>475</v>
       </c>
       <c r="D67" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="E67" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C68" t="n">
-        <v>4701</v>
+        <v>4357</v>
       </c>
       <c r="D68" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="E68" t="n">
-        <v>23.5</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C69" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D69" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C70" t="n">
-        <v>2066</v>
+        <v>1884</v>
       </c>
       <c r="D70" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="E70" t="n">
-        <v>10.33</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C71" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D71" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="E71" t="n">
         <v>0.14</v>
@@ -2550,135 +2556,135 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C72" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D72" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="E72" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B73" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" t="n">
         <v>89</v>
       </c>
-      <c r="C73" t="n">
-        <v>103</v>
-      </c>
       <c r="D73" t="n">
-        <v>20007</v>
+        <v>18319</v>
       </c>
       <c r="E73" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C74" t="n">
-        <v>1864</v>
+        <v>1711</v>
       </c>
       <c r="D74" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="E74" t="n">
-        <v>65.47</v>
+        <v>65.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C75" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D75" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="E75" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C76" t="n">
-        <v>666</v>
+        <v>611</v>
       </c>
       <c r="D76" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="E76" t="n">
-        <v>23.39</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="E77" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C78" t="n">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="D78" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="E78" t="n">
-        <v>7.52</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" t="n">
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="E79" t="n">
         <v>0.11</v>
@@ -2686,36 +2692,36 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C80" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D80" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="E80" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D81" t="n">
-        <v>2847</v>
+        <v>2610</v>
       </c>
       <c r="E81" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -2731,27 +2737,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -2771,7 +2777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -2791,7 +2797,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -2811,7 +2817,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="b">
         <v>0</v>
@@ -2831,7 +2837,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="b">
         <v>0</v>
@@ -2851,7 +2857,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="b">
         <v>0</v>
@@ -2871,7 +2877,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="b">
         <v>0</v>
@@ -2902,21 +2908,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" t="n">
         <v>1074796</v>
@@ -2930,7 +2936,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" t="n">
         <v>1074782</v>
@@ -2955,24 +2961,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="n">
         <v>65664</v>
@@ -2984,12 +2990,12 @@
         <v>0.01</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" t="n">
         <v>119237</v>
@@ -3001,12 +3007,12 @@
         <v>0.01</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
         <v>173863</v>
@@ -3018,12 +3024,12 @@
         <v>0.01</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" t="n">
         <v>183260</v>
@@ -3035,12 +3041,12 @@
         <v>0.01</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
         <v>184103</v>
@@ -3052,12 +3058,12 @@
         <v>0.02</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
         <v>156788</v>
@@ -3069,12 +3075,12 @@
         <v>0.02</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>111331</v>
@@ -3086,12 +3092,12 @@
         <v>0.02</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -3103,12 +3109,12 @@
         <v>0.01</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" t="n">
         <v>20014</v>
@@ -3120,12 +3126,12 @@
         <v>0.01</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="n">
         <v>2847</v>
@@ -3137,12 +3143,12 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="n">
         <v>65664</v>
@@ -3154,12 +3160,12 @@
         <v>0.01</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="n">
         <v>119237</v>
@@ -3171,12 +3177,12 @@
         <v>0.01</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
         <v>173863</v>
@@ -3188,12 +3194,12 @@
         <v>0.01</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="n">
         <v>183260</v>
@@ -3205,12 +3211,12 @@
         <v>0.01</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" t="n">
         <v>184103</v>
@@ -3222,12 +3228,12 @@
         <v>0.02</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" t="n">
         <v>156788</v>
@@ -3239,12 +3245,12 @@
         <v>0.02</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="n">
         <v>111331</v>
@@ -3256,12 +3262,12 @@
         <v>0.02</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="n">
         <v>57887</v>
@@ -3273,12 +3279,12 @@
         <v>0.01</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" t="n">
         <v>20014</v>
@@ -3290,12 +3296,12 @@
         <v>0.02</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" t="n">
         <v>2847</v>
@@ -3307,12 +3313,12 @@
         <v>0</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="n">
         <v>65664</v>
@@ -3324,12 +3330,12 @@
         <v>0.01</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" t="n">
         <v>119237</v>
@@ -3341,12 +3347,12 @@
         <v>0.01</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" t="n">
         <v>173863</v>
@@ -3358,12 +3364,12 @@
         <v>0.01</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" t="n">
         <v>183260</v>
@@ -3375,12 +3381,12 @@
         <v>0.02</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
         <v>184103</v>
@@ -3392,12 +3398,12 @@
         <v>0.02</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" t="n">
         <v>156788</v>
@@ -3409,12 +3415,12 @@
         <v>0.02</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" t="n">
         <v>111331</v>
@@ -3426,12 +3432,12 @@
         <v>0.03</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" t="n">
         <v>57887</v>
@@ -3443,12 +3449,12 @@
         <v>0.01</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30" t="n">
         <v>20014</v>
@@ -3460,12 +3466,12 @@
         <v>0.03</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" t="n">
         <v>2847</v>
@@ -3477,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3493,21 +3499,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="n">
         <v>65664</v>
@@ -3521,7 +3527,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" t="n">
         <v>119237</v>
@@ -3535,7 +3541,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
         <v>173863</v>
@@ -3549,7 +3555,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" t="n">
         <v>183260</v>
@@ -3563,7 +3569,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
         <v>184103</v>
@@ -3577,7 +3583,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
         <v>156788</v>
@@ -3591,7 +3597,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>111331</v>
@@ -3605,7 +3611,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" t="n">
         <v>57887</v>
@@ -3619,7 +3625,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" t="n">
         <v>20014</v>
@@ -3633,7 +3639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="n">
         <v>2847</v>
@@ -3658,189 +3664,189 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3856,189 +3862,189 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -4054,24 +4060,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="n">
         <v>47379</v>
@@ -4080,7 +4086,7 @@
         <v>331</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E2" t="n">
         <v>0.7</v>
@@ -4088,7 +4094,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" t="n">
         <v>85902</v>
@@ -4097,7 +4103,7 @@
         <v>477</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E3" t="n">
         <v>0.56</v>
@@ -4105,7 +4111,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
         <v>125868</v>
@@ -4114,7 +4120,7 @@
         <v>1085</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E4" t="n">
         <v>0.86</v>
@@ -4122,7 +4128,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" t="n">
         <v>131720</v>
@@ -4131,7 +4137,7 @@
         <v>2191</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E5" t="n">
         <v>1.66</v>
@@ -4139,7 +4145,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" t="n">
         <v>132112</v>
@@ -4148,7 +4154,7 @@
         <v>5234</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E6" t="n">
         <v>3.96</v>
@@ -4156,7 +4162,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
         <v>113362</v>
@@ -4165,7 +4171,7 @@
         <v>9497</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E7" t="n">
         <v>8.38</v>
@@ -4173,7 +4179,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>81282</v>
@@ -4182,7 +4188,7 @@
         <v>10864</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E8" t="n">
         <v>13.37</v>
@@ -4190,7 +4196,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" t="n">
         <v>41851</v>
@@ -4199,7 +4205,7 @@
         <v>6592</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="n">
         <v>15.75</v>
@@ -4207,7 +4213,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" t="n">
         <v>14542</v>
@@ -4216,7 +4222,7 @@
         <v>2157</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" t="n">
         <v>14.83</v>
@@ -4224,7 +4230,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="n">
         <v>2054</v>
@@ -4233,7 +4239,7 @@
         <v>233</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" t="n">
         <v>11.34</v>
@@ -4241,7 +4247,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="n">
         <v>47379</v>
@@ -4250,7 +4256,7 @@
         <v>485</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="n">
         <v>1.02</v>
@@ -4258,7 +4264,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="n">
         <v>85902</v>
@@ -4267,7 +4273,7 @@
         <v>504</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E13" t="n">
         <v>0.59</v>
@@ -4275,7 +4281,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
         <v>125868</v>
@@ -4284,7 +4290,7 @@
         <v>2096</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E14" t="n">
         <v>1.67</v>
@@ -4292,7 +4298,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="n">
         <v>131720</v>
@@ -4301,7 +4307,7 @@
         <v>6079</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E15" t="n">
         <v>4.62</v>
@@ -4309,7 +4315,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" t="n">
         <v>132112</v>
@@ -4318,7 +4324,7 @@
         <v>15066</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E16" t="n">
         <v>11.4</v>
@@ -4326,7 +4332,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" t="n">
         <v>113362</v>
@@ -4335,7 +4341,7 @@
         <v>23618</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E17" t="n">
         <v>20.83</v>
@@ -4343,7 +4349,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" t="n">
         <v>81282</v>
@@ -4352,7 +4358,7 @@
         <v>24351</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E18" t="n">
         <v>29.96</v>
@@ -4360,7 +4366,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="n">
         <v>41851</v>
@@ -4369,7 +4375,7 @@
         <v>15053</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E19" t="n">
         <v>35.97</v>
@@ -4377,7 +4383,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" t="n">
         <v>14542</v>
@@ -4386,7 +4392,7 @@
         <v>5544</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E20" t="n">
         <v>38.12</v>
@@ -4394,7 +4400,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" t="n">
         <v>2054</v>
@@ -4403,7 +4409,7 @@
         <v>734</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E21" t="n">
         <v>35.74</v>
@@ -4411,7 +4417,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="n">
         <v>47379</v>
@@ -4420,7 +4426,7 @@
         <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E22" t="n">
         <v>0.3</v>
@@ -4428,7 +4434,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" t="n">
         <v>85902</v>
@@ -4437,7 +4443,7 @@
         <v>218</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E23" t="n">
         <v>0.25</v>
@@ -4445,7 +4451,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" t="n">
         <v>125868</v>
@@ -4454,7 +4460,7 @@
         <v>339</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E24" t="n">
         <v>0.27</v>
@@ -4462,7 +4468,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" t="n">
         <v>131720</v>
@@ -4471,7 +4477,7 @@
         <v>435</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E25" t="n">
         <v>0.33</v>
@@ -4479,7 +4485,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
         <v>132112</v>
@@ -4488,7 +4494,7 @@
         <v>560</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E26" t="n">
         <v>0.42</v>
@@ -4496,7 +4502,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" t="n">
         <v>113362</v>
@@ -4505,7 +4511,7 @@
         <v>664</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E27" t="n">
         <v>0.59</v>
@@ -4513,7 +4519,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" t="n">
         <v>81282</v>
@@ -4522,7 +4528,7 @@
         <v>637</v>
       </c>
       <c r="D28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E28" t="n">
         <v>0.78</v>
@@ -4530,7 +4536,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" t="n">
         <v>41851</v>
@@ -4539,7 +4545,7 @@
         <v>442</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E29" t="n">
         <v>1.06</v>
@@ -4547,7 +4553,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B30" t="n">
         <v>14542</v>
@@ -4556,7 +4562,7 @@
         <v>264</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E30" t="n">
         <v>1.82</v>
@@ -4564,7 +4570,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" t="n">
         <v>2054</v>
@@ -4573,7 +4579,7 @@
         <v>38</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E31" t="n">
         <v>1.85</v>
@@ -4592,27 +4598,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
         <v>46623</v>
@@ -4626,10 +4632,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" t="n">
         <v>191</v>
@@ -4643,10 +4649,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
         <v>337</v>
@@ -4660,10 +4666,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="n">
         <v>78</v>
@@ -4677,10 +4683,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="n">
         <v>86</v>
@@ -4694,10 +4700,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
@@ -4711,10 +4717,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
@@ -4728,10 +4734,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>52</v>
@@ -4745,10 +4751,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
         <v>84930</v>
@@ -4762,10 +4768,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="n">
         <v>342</v>
@@ -4779,10 +4785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" t="n">
         <v>364</v>
@@ -4796,10 +4802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" t="n">
         <v>119</v>
@@ -4813,10 +4819,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" t="n">
         <v>48</v>
@@ -4830,10 +4836,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
@@ -4847,10 +4853,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
@@ -4864,10 +4870,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="n">
         <v>80</v>
@@ -4881,10 +4887,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C18" t="n">
         <v>122895</v>
@@ -4898,10 +4904,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" t="n">
         <v>703</v>
@@ -4915,10 +4921,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" t="n">
         <v>1702</v>
@@ -4932,10 +4938,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C21" t="n">
         <v>163</v>
@@ -4949,10 +4955,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C22" t="n">
         <v>229</v>
@@ -4966,10 +4972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" t="n">
         <v>11</v>
@@ -4983,10 +4989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="n">
         <v>23</v>
@@ -5000,10 +5006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" t="n">
         <v>142</v>
@@ -5017,10 +5023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" t="n">
         <v>124127</v>
@@ -5034,10 +5040,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" t="n">
         <v>1278</v>
@@ -5051,10 +5057,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" t="n">
         <v>5135</v>
@@ -5068,10 +5074,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" t="n">
         <v>210</v>
@@ -5085,10 +5091,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C30" t="n">
         <v>745</v>
@@ -5102,10 +5108,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" t="n">
         <v>26</v>
@@ -5119,10 +5125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" t="n">
         <v>57</v>
@@ -5136,10 +5142,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C33" t="n">
         <v>142</v>
@@ -5153,10 +5159,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" t="n">
         <v>114327</v>
@@ -5170,10 +5176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" t="n">
         <v>2447</v>
@@ -5187,10 +5193,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" t="n">
         <v>12185</v>
@@ -5204,10 +5210,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" t="n">
         <v>245</v>
@@ -5221,10 +5227,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" t="n">
         <v>2593</v>
@@ -5238,10 +5244,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" t="n">
         <v>27</v>
@@ -5255,10 +5261,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C40" t="n">
         <v>121</v>
@@ -5272,10 +5278,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" t="n">
         <v>167</v>
@@ -5289,10 +5295,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C42" t="n">
         <v>86175</v>
@@ -5306,10 +5312,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" t="n">
         <v>3263</v>
@@ -5323,10 +5329,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C44" t="n">
         <v>17296</v>
@@ -5340,10 +5346,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C45" t="n">
         <v>232</v>
@@ -5357,10 +5363,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C46" t="n">
         <v>5964</v>
@@ -5374,10 +5380,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" t="n">
         <v>74</v>
@@ -5391,10 +5397,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C48" t="n">
         <v>162</v>
@@ -5408,10 +5414,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C49" t="n">
         <v>196</v>
@@ -5425,10 +5431,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C50" t="n">
         <v>53960</v>
@@ -5442,10 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C51" t="n">
         <v>2745</v>
@@ -5459,10 +5465,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C52" t="n">
         <v>16107</v>
@@ -5476,10 +5482,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C53" t="n">
         <v>182</v>
@@ -5493,10 +5499,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C54" t="n">
         <v>7833</v>
@@ -5510,10 +5516,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C55" t="n">
         <v>44</v>
@@ -5527,10 +5533,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C56" t="n">
         <v>169</v>
@@ -5544,10 +5550,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C57" t="n">
         <v>242</v>
@@ -5561,10 +5567,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C58" t="n">
         <v>25295</v>
@@ -5578,10 +5584,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C59" t="n">
         <v>1360</v>
@@ -5595,10 +5601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C60" t="n">
         <v>9721</v>
@@ -5612,10 +5618,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C61" t="n">
         <v>96</v>
@@ -5629,10 +5635,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C62" t="n">
         <v>5033</v>
@@ -5646,10 +5652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C63" t="n">
         <v>47</v>
@@ -5663,10 +5669,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C64" t="n">
         <v>147</v>
@@ -5680,10 +5686,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C65" t="n">
         <v>152</v>
@@ -5697,10 +5703,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C66" t="n">
         <v>8511</v>
@@ -5714,10 +5720,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C67" t="n">
         <v>416</v>
@@ -5731,10 +5737,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C68" t="n">
         <v>3719</v>
@@ -5748,10 +5754,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C69" t="n">
         <v>49</v>
@@ -5765,10 +5771,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C70" t="n">
         <v>1632</v>
@@ -5782,10 +5788,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C71" t="n">
         <v>22</v>
@@ -5799,10 +5805,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C72" t="n">
         <v>106</v>
@@ -5816,10 +5822,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C73" t="n">
         <v>87</v>
@@ -5833,10 +5839,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C74" t="n">
         <v>1267</v>
@@ -5850,10 +5856,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C75" t="n">
         <v>46</v>
@@ -5867,10 +5873,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C76" t="n">
         <v>528</v>
@@ -5884,10 +5890,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C77" t="n">
         <v>5</v>
@@ -5901,10 +5907,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C78" t="n">
         <v>175</v>
@@ -5918,10 +5924,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" t="n">
         <v>2</v>
@@ -5935,10 +5941,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C80" t="n">
         <v>21</v>
@@ -5952,10 +5958,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C81" t="n">
         <v>10</v>
